--- a/data/trans_camb/P6901-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 25,05</t>
+          <t>-11,33; 25,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 17,25</t>
+          <t>-23,17; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 7,74</t>
+          <t>-30,51; 7,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 20,18</t>
+          <t>-20,92; 22,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 20,6</t>
+          <t>-17,93; 22,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 21,94</t>
+          <t>-15,0; 22,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 16,47</t>
+          <t>-9,0; 18,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 12,6</t>
+          <t>-14,48; 14,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 9,29</t>
+          <t>-16,8; 8,77</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 53,94</t>
+          <t>-16,99; 55,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 35,7</t>
+          <t>-36,02; 32,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,53; 15,6</t>
+          <t>-46,59; 16,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 39,46</t>
+          <t>-29,48; 48,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 44,84</t>
+          <t>-24,95; 46,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 47,44</t>
+          <t>-21,54; 48,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 31,33</t>
+          <t>-14,6; 35,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 24,54</t>
+          <t>-22,5; 27,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 17,52</t>
+          <t>-26,06; 16,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 44,68</t>
+          <t>1,64; 45,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 46,6</t>
+          <t>0,98; 46,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 26,92</t>
+          <t>-15,31; 25,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 8,51</t>
+          <t>-34,85; 8,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 19,36</t>
+          <t>-10,57; 20,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,64; -12,16</t>
+          <t>-46,94; -10,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 22,51</t>
+          <t>-8,08; 21,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 29,28</t>
+          <t>2,54; 30,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 2,4</t>
+          <t>-25,28; 4,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 121,32</t>
+          <t>5,33; 120,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 128,76</t>
+          <t>3,46; 124,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 79,97</t>
+          <t>-24,66; 67,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 10,64</t>
+          <t>-40,27; 10,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 25,51</t>
+          <t>-11,67; 26,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,64; -16,29</t>
+          <t>-53,04; -14,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 37,83</t>
+          <t>-11,75; 36,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 50,46</t>
+          <t>4,02; 53,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 4,05</t>
+          <t>-34,78; 7,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 2,92</t>
+          <t>-22,23; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 2,62</t>
+          <t>-24,98; 2,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 3,58</t>
+          <t>-26,05; 3,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 37,36</t>
+          <t>-8,52; 38,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 34,8</t>
+          <t>-21,73; 34,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 28,84</t>
+          <t>-21,95; 28,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 6,59</t>
+          <t>-14,53; 6,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 5,99</t>
+          <t>-22,59; 4,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 5,19</t>
+          <t>-22,33; 3,81</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 3,92</t>
+          <t>-26,37; 5,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 3,69</t>
+          <t>-29,82; 3,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 4,83</t>
+          <t>-31,87; 3,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 66,3</t>
+          <t>-9,08; 67,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 62,61</t>
+          <t>-23,35; 54,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 49,02</t>
+          <t>-24,29; 48,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 8,7</t>
+          <t>-17,64; 9,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 7,52</t>
+          <t>-27,32; 5,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 6,23</t>
+          <t>-27,08; 4,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 6,23</t>
+          <t>-13,49; 5,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 7,78</t>
+          <t>-9,96; 7,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 11,17</t>
+          <t>-6,56; 11,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 26,35</t>
+          <t>-5,45; 26,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,74; 35,42</t>
+          <t>6,32; 35,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 23,59</t>
+          <t>-4,6; 22,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 7,96</t>
+          <t>-7,82; 8,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 12,37</t>
+          <t>-2,4; 12,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 10,33</t>
+          <t>-3,73; 9,89</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 8,16</t>
+          <t>-16,13; 7,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 10,25</t>
+          <t>-11,95; 10,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 14,75</t>
+          <t>-8,02; 14,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 43,73</t>
+          <t>-7,15; 42,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 59,01</t>
+          <t>8,03; 61,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 40,82</t>
+          <t>-5,8; 36,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 10,81</t>
+          <t>-9,6; 11,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 16,47</t>
+          <t>-2,92; 16,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 13,45</t>
+          <t>-4,58; 13,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 14,76</t>
+          <t>-15,32; 14,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 11,9</t>
+          <t>-14,68; 12,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 16,72</t>
+          <t>-11,58; 17,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 4,6</t>
+          <t>-25,24; 3,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 12,17</t>
+          <t>-9,49; 12,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 11,66</t>
+          <t>-11,17; 11,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 6,78</t>
+          <t>-14,76; 5,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 7,89</t>
+          <t>-9,56; 8,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 12,4</t>
+          <t>-7,74; 11,52</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 19,66</t>
+          <t>-17,51; 19,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 15,3</t>
+          <t>-16,15; 16,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 22,25</t>
+          <t>-12,52; 22,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 5,14</t>
+          <t>-27,18; 4,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 14,5</t>
+          <t>-10,25; 14,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 13,76</t>
+          <t>-11,99; 14,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 8,04</t>
+          <t>-16,29; 6,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 9,58</t>
+          <t>-10,21; 9,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 15,31</t>
+          <t>-8,43; 13,89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,43</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,76; 5,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,64; 5,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,88; 3,84</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,69; 7,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,84; 14,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,35; 9,65</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,57; 4,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,14; 7,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,38; 5,17</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-1,03%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,75%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,1%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,57%</t>
         </is>
       </c>
     </row>
@@ -1863,282 +1863,65 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,69; 7,84</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,56; 7,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,83; 5,18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,46; 9,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,96; 19,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,92; 13,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,0; 5,99</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,75; 9,87</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,87; 7,02</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>7,01</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-6,96; 5,26</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-6,95; 5,86</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-8,8; 3,93</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-8,01; 8,13</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-0,85; 14,08</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 8,9</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-5,31; 4,71</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 7,34</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-5,4; 5,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>-1,03%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-0,75%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-3,1%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-0,3%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-0,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-8,98; 7,15</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-8,87; 8,13</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-11,29; 5,39</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-9,75; 10,99</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>-0,58; 19,53</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-8,9; 12,04</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-6,7; 6,4</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-3,08; 9,93</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-6,96; 7,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>

--- a/data/trans_camb/P6901-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-11,35</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,38</t>
+          <t>-1,04</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 25,41</t>
+          <t>-12,11; 24,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 15,88</t>
+          <t>-25,13; 17,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 7,42</t>
+          <t>-26,26; 11,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 22,37</t>
+          <t>-23,2; 19,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 22,23</t>
+          <t>-19,06; 22,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 22,04</t>
+          <t>-14,96; 19,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 18,31</t>
+          <t>-10,06; 16,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 14,45</t>
+          <t>-15,63; 12,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 8,77</t>
+          <t>-14,01; 11,79</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-19,67%</t>
+          <t>-10,69%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-5,75%</t>
+          <t>-1,76%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 55,21</t>
+          <t>-19,56; 51,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,02; 32,27</t>
+          <t>-39,01; 36,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 16,19</t>
+          <t>-40,55; 22,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 48,37</t>
+          <t>-32,66; 43,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 46,87</t>
+          <t>-26,4; 45,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 48,47</t>
+          <t>-21,02; 39,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 35,36</t>
+          <t>-15,44; 33,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 27,69</t>
+          <t>-24,49; 24,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 16,93</t>
+          <t>-21,37; 23,55</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-29,2</t>
+          <t>-29,01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,58</t>
+          <t>-11,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 45,32</t>
+          <t>1,17; 46,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 46,58</t>
+          <t>3,27; 46,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 25,45</t>
+          <t>-15,66; 27,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 8,84</t>
+          <t>-35,32; 9,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 20,28</t>
+          <t>-11,43; 20,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,94; -10,59</t>
+          <t>-45,67; -12,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 21,86</t>
+          <t>-8,39; 22,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 30,68</t>
+          <t>2,16; 28,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 4,66</t>
+          <t>-26,21; 1,68</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-34,24%</t>
+          <t>-34,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-17,09%</t>
+          <t>-17,24%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 120,86</t>
+          <t>3,52; 125,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 124,48</t>
+          <t>6,71; 131,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 67,77</t>
+          <t>-26,06; 80,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 10,8</t>
+          <t>-38,93; 11,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 26,97</t>
+          <t>-12,38; 27,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,04; -14,29</t>
+          <t>-52,14; -15,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 36,6</t>
+          <t>-10,71; 37,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 53,83</t>
+          <t>3,42; 48,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 7,73</t>
+          <t>-35,36; 2,83</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-10,08</t>
+          <t>-8,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,66</t>
+          <t>-6,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 3,77</t>
+          <t>-22,61; 3,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 2,26</t>
+          <t>-25,46; 3,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 3,51</t>
+          <t>-23,63; 5,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 38,38</t>
+          <t>-9,11; 35,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 34,88</t>
+          <t>-22,33; 33,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 28,6</t>
+          <t>-20,12; 28,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 6,86</t>
+          <t>-14,06; 7,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 4,12</t>
+          <t>-22,76; 3,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 3,81</t>
+          <t>-18,38; 6,68</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,6%</t>
+          <t>-10,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,57%</t>
+          <t>-7,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 5,1</t>
+          <t>-27,01; 4,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 3,02</t>
+          <t>-30,41; 4,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,87; 3,92</t>
+          <t>-28,83; 7,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 67,68</t>
+          <t>-7,93; 62,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 54,41</t>
+          <t>-25,48; 52,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 48,49</t>
+          <t>-22,41; 47,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 9,22</t>
+          <t>-16,8; 9,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 5,48</t>
+          <t>-26,69; 5,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 4,93</t>
+          <t>-21,74; 8,91</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,79</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>3,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 5,95</t>
+          <t>-13,65; 6,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 7,77</t>
+          <t>-10,87; 7,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 11,1</t>
+          <t>-5,09; 11,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 26,14</t>
+          <t>-5,16; 26,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 35,46</t>
+          <t>3,94; 33,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 22,06</t>
+          <t>-5,43; 22,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 8,47</t>
+          <t>-8,43; 7,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 12,27</t>
+          <t>-1,54; 12,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 9,89</t>
+          <t>-3,96; 10,28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 7,7</t>
+          <t>-16,4; 7,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 10,02</t>
+          <t>-12,93; 10,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 14,7</t>
+          <t>-6,1; 14,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 42,82</t>
+          <t>-6,21; 44,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,03; 61,71</t>
+          <t>4,89; 56,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 36,13</t>
+          <t>-6,98; 37,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 11,24</t>
+          <t>-10,46; 10,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 16,53</t>
+          <t>-1,91; 17,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 13,2</t>
+          <t>-4,82; 13,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>5,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 14,66</t>
+          <t>-13,57; 13,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 12,78</t>
+          <t>-13,35; 13,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 17,08</t>
+          <t>-6,24; 18,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 3,83</t>
+          <t>-25,21; 4,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 12,11</t>
+          <t>-9,54; 13,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 11,69</t>
+          <t>-3,55; 12,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 5,45</t>
+          <t>-14,32; 5,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 8,11</t>
+          <t>-9,94; 8,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 11,52</t>
+          <t>-1,96; 12,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 19,44</t>
+          <t>-15,09; 17,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 16,95</t>
+          <t>-14,91; 16,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 22,43</t>
+          <t>-6,88; 24,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 4,33</t>
+          <t>-26,43; 5,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 14,42</t>
+          <t>-10,02; 15,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 14,04</t>
+          <t>-3,71; 15,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 6,5</t>
+          <t>-15,74; 6,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 9,61</t>
+          <t>-10,88; 9,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 13,89</t>
+          <t>-2,18; 14,96</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,66</t>
+          <t>-7,46; 5,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,08</t>
+          <t>-6,98; 6,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 3,84</t>
+          <t>-6,31; 5,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 7,15</t>
+          <t>-8,41; 8,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 14,08</t>
+          <t>-1,15; 14,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 9,65</t>
+          <t>-6,57; 7,1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,38</t>
+          <t>-5,67; 4,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,26</t>
+          <t>-2,77; 7,33</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 5,17</t>
+          <t>-4,41; 4,62</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-3,1%</t>
+          <t>-0,29%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>-0,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-0,57%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 7,84</t>
+          <t>-9,69; 7,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 7,08</t>
+          <t>-8,9; 8,34</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 5,18</t>
+          <t>-8,24; 7,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 9,64</t>
+          <t>-10,44; 10,94</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 19,26</t>
+          <t>-1,39; 20,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 13,11</t>
+          <t>-8,03; 9,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 5,99</t>
+          <t>-7,1; 5,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 9,87</t>
+          <t>-3,54; 9,96</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 7,02</t>
+          <t>-5,65; 6,3</t>
         </is>
       </c>
     </row>
